--- a/docs/downloads/经营分_津河省区__津东片区_2026-10-19.xlsx
+++ b/docs/downloads/经营分_津河省区__津东片区_2026-10-19.xlsx
@@ -12,7 +12,7 @@
     <sheet name="匹配异常" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'门店经营分'!$A$1:$V$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'匹配异常'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -771,33 +771,33 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>6601142402113619976</t>
+          <t>7288242743682271284</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>锦江之星天津滨海国际机场华明高新区酒店</t>
+          <t>维也纳国际酒店(天津站五大道店)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>锦江之星(天津机场店)</t>
+          <t>维也纳国际酒店(天津站五大道店)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>-22</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,附加分,拿收益</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -807,25 +807,25 @@
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>30</v>
       </c>
       <c r="O3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="n">
         <v>20</v>
@@ -855,43 +855,43 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>7290826708838516777</t>
+          <t>6601142402113619976</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>丽怡酒店（天津空港滨海国际机场店）</t>
+          <t>锦江之星天津滨海国际机场华明高新区酒店</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>丽怡酒店(天津空港滨海国际机场店)</t>
+          <t>锦江之星(天津机场店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L4" t="n">
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -903,7 +903,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -939,17 +939,17 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6764504457100199943</t>
+          <t>7290826708838516777</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0天津滨海国际机场空港自贸区店）</t>
+          <t>丽怡酒店（天津空港滨海国际机场店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0天津滨海国际机场空港自贸区店)</t>
+          <t>丽怡酒店(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
@@ -987,7 +987,7 @@
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1020,50 +1020,46 @@
           <t>津东片区</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>6601142168541202436</t>
+          <t>6764504457100199943</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7天酒店（天津东丽开发区轻轨站店）</t>
+          <t>维也纳酒店（5.0天津滨海国际机场空港自贸区店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7天酒店(天津东丽开发区轻轨站店)</t>
+          <t>维也纳酒店(5.0天津滨海国际机场空港自贸区店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="I6" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1075,7 +1071,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1115,17 +1111,17 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7298933210174457883</t>
+          <t>6601142168541202436</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>喆啡酒店天津东丽开发区滨海国际机场店</t>
+          <t>7天酒店（天津东丽开发区轻轨站店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津东丽开发区滨海国际机场店)</t>
+          <t>7天酒店(天津东丽开发区轻轨站店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1134,36 +1130,36 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>稳房源,提质量,拿收益</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>稳房源,提质量,拿收益</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>10</v>
-      </c>
-      <c r="M7" t="n">
-        <v>22</v>
-      </c>
       <c r="N7" t="n">
         <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1196,20 +1192,24 @@
           <t>津东片区</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>6601139036411136007</t>
+          <t>7298933210174457883</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>希岸酒店天津火车站津湾广场滨江道店</t>
+          <t>喆啡酒店天津东丽开发区滨海国际机场店</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>希岸酒店(天津火车站津湾广场滨江道店)</t>
+          <t>喆啡酒店(天津东丽开发区滨海国际机场店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1235,7 +1235,7 @@
         <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N8" t="n">
         <v>30</v>
@@ -1247,7 +1247,7 @@
         <v>30</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R8" t="n">
         <v>30</v>
@@ -1280,24 +1280,20 @@
           <t>津东片区</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>天津市</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6664116911141406733</t>
+          <t>6601139036411136007</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店天津华明滨海国际机场店</t>
+          <t>希岸酒店天津火车站津湾广场滨江道店</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>希岸酒店(天津华明滨海国际机场店)</t>
+          <t>希岸酒店(天津火车站津湾广场滨江道店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1306,7 +1302,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1323,7 +1319,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1375,29 +1371,29 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6763895812595468296</t>
+          <t>6664116911141406733</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>希岸酒店天津滨江道和平路地铁站劝业场店</t>
+          <t>希岸·轻雅酒店天津华明滨海国际机场店</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>希岸酒店(天津滨江道和平路地铁站劝业场店)</t>
+          <t>希岸酒店(天津华明滨海国际机场店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1463,29 +1459,29 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>6845044439950411791</t>
+          <t>6763895812595468296</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津东丽开发区地铁站店</t>
+          <t>希岸酒店天津滨江道和平路地铁站劝业场店</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津东丽开发区地铁站店)</t>
+          <t>希岸酒店(天津滨江道和平路地铁站劝业场店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1551,22 +1547,22 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7276268799819515956</t>
+          <t>6845044439950411791</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津华明滨海国际机场店</t>
+          <t>麗枫酒店·天津东丽开发区地铁站店</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津华明滨海国际机场店)</t>
+          <t>麗枫酒店(天津东丽开发区地铁站店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1639,17 +1635,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>6738219457916733453</t>
+          <t>7276268799819515956</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>麗枫酒店·天津大悦城鼓楼地铁站店</t>
+          <t>麗枫酒店·天津华明滨海国际机场店</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津大悦城鼓楼地铁站店)</t>
+          <t>麗枫酒店(天津华明滨海国际机场店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1727,26 +1723,26 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>6601175799364061188</t>
+          <t>6738219457916733453</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7天优品（天津成林道万新村武警医院店）</t>
+          <t>麗枫酒店·天津大悦城鼓楼地铁站店</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7天优品酒店(天津成林道万新村武警医院店)</t>
+          <t>麗枫酒店(天津大悦城鼓楼地铁站店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1763,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N14" t="n">
         <v>30</v>
@@ -1775,7 +1771,7 @@
         <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1815,22 +1811,22 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6601136810775021582</t>
+          <t>6601175799364061188</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IU酒店·天津机场空港经济区店</t>
+          <t>7天优品（天津成林道万新村武警医院店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>iu酒店(天津机场空港经济区店)</t>
+          <t>7天优品酒店(天津成林道万新村武警医院店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1851,7 +1847,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
@@ -1863,7 +1859,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1903,17 +1899,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6824286894663206920</t>
+          <t>6601136810775021582</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津古文化街鼓楼地铁站店）</t>
+          <t>IU酒店·天津机场空港经济区店</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津古文化街鼓楼地铁站店)</t>
+          <t>iu酒店(天津机场空港经济区店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1922,10 +1918,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1939,7 +1935,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
@@ -1951,7 +1947,7 @@
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -1991,29 +1987,29 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6870867024571009031</t>
+          <t>6824286894663206920</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津滨海国际机场武警医院店）</t>
+          <t>喆啡酒店（天津古文化街鼓楼地铁站店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津滨海国际机场武警医院店)</t>
+          <t>喆啡酒店(天津古文化街鼓楼地铁站店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>92</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2079,17 +2075,17 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7118338141840214028</t>
+          <t>6870867024571009031</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>喆啡酒店（天津海光寺眼科医院店）</t>
+          <t>喆啡酒店（天津滨海国际机场武警医院店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津海光寺眼科医院店)</t>
+          <t>喆啡酒店(天津滨海国际机场武警医院店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2098,18 +2094,18 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L18" t="n">
         <v>10</v>
@@ -2121,7 +2117,7 @@
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
@@ -2167,17 +2163,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6886081243822491661</t>
+          <t>7118338141840214028</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店（天津古文化街鼓楼地铁站店）</t>
+          <t>喆啡酒店（天津海光寺眼科医院店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(天津大悦城鼓楼地铁站店)</t>
+          <t>喆啡酒店(天津海光寺眼科医院店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2189,7 +2185,7 @@
         <v>93</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2255,17 +2251,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7048813080796465159</t>
+          <t>6886081243822491661</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7天优品（天津北方五金城店）</t>
+          <t>希岸·轻雅酒店（天津古文化街鼓楼地铁站店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7天优品酒店(北方五金城店)</t>
+          <t>希岸·轻雅酒店(天津大悦城鼓楼地铁站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2274,30 +2270,30 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
       </c>
       <c r="M20" t="n">
+        <v>22</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30</v>
+      </c>
+      <c r="O20" t="n">
         <v>25</v>
-      </c>
-      <c r="N20" t="n">
-        <v>30</v>
-      </c>
-      <c r="O20" t="n">
-        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
@@ -2343,22 +2339,22 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7506790632631830547</t>
+          <t>7048813080796465159</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
+          <t>7天优品（天津北方五金城店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
+          <t>7天优品酒店(北方五金城店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2385,13 +2381,13 @@
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2431,37 +2427,37 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7132466961895819298</t>
+          <t>7506790632631830547</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>麗枫酒店天津万科民和巷店</t>
+          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>麗枫酒店(天津东丽万科民和巷店)</t>
+          <t>非繁城品酒店(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
         <v>10</v>
@@ -2479,7 +2475,7 @@
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2519,17 +2515,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>6622218143370577924</t>
+          <t>7132466961895819298</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳酒店天津海光寺眼科医院店</t>
+          <t>麗枫酒店天津万科民和巷店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津海光寺眼科医院店)</t>
+          <t>麗枫酒店(天津东丽万科民和巷店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2538,24 +2534,24 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
@@ -2607,17 +2603,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601138246594332675</t>
+          <t>6622218143370577924</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>维也纳酒店（天津机场文会路店）</t>
+          <t>维也纳酒店天津海光寺眼科医院店</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>维也纳酒店(天津机场华明二店)</t>
+          <t>维也纳酒店(天津海光寺眼科医院店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2629,11 +2625,11 @@
         <v>97</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2649,13 +2645,13 @@
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2695,17 +2691,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6601141512925349896</t>
+          <t>6601138246594332675</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>锦江之星（新品）天津空港酒店</t>
+          <t>维也纳酒店（天津机场文会路店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>锦江之星(天津空港酒店)</t>
+          <t>维也纳酒店(天津机场华明二店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2714,10 +2710,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2731,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2783,17 +2779,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7237774118546851855</t>
+          <t>6601141512925349896</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版天津东丽开发区地铁站店）</t>
+          <t>锦江之星（新品）天津空港酒店</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(5.0版天津东丽开发区地铁站店)</t>
+          <t>锦江之星(天津空港酒店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2802,7 +2798,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2819,7 +2815,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2831,7 +2827,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2871,33 +2867,33 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7432536549700405263</t>
+          <t>7237774118546851855</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（3.0版天津空港滨海国际机场店）</t>
+          <t>维也纳国际酒店（5.0版天津东丽开发区地铁站店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(天津空港滨海国际机场店)</t>
+          <t>维也纳国际酒店(5.0版天津东丽开发区地铁站店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2907,7 +2903,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2919,7 +2915,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2959,33 +2955,33 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7520175585272793151</t>
+          <t>7432536549700405263</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>麗枫酒店（天津滨海国际机场空港商务园店）</t>
+          <t>凯里亚德酒店（3.0版天津空港滨海国际机场店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>LAVANDE麗枫酒店(天津滨海国际机场空港商务园店)</t>
+          <t>凯里亚德酒店(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>105</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2995,19 +2991,19 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3047,33 +3043,33 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>6978083705865406505</t>
+          <t>7520175585272793151</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>天津空港滨海国际机场丽柏酒店</t>
+          <t>麗枫酒店（天津滨海国际机场空港商务园店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>丽柏酒店Park Inn(天津空港滨海国际机场店)</t>
+          <t>LAVANDE麗枫酒店(天津滨海国际机场空港商务园店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3083,13 +3079,13 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
@@ -3135,22 +3131,22 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>6601132334718650382</t>
+          <t>6978083705865406505</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（天津站滨江道步行街店）</t>
+          <t>天津空港滨海国际机场丽柏酒店</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(天津站滨江道步行街店)</t>
+          <t>丽柏酒店Park Inn(天津空港滨海国际机场店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -3161,7 +3157,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3171,19 +3167,19 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3223,17 +3219,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7582047719217170486</t>
+          <t>6601132334718650382</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津站津湾广场店)</t>
+          <t>维也纳国际酒店（天津站滨江道步行街店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>喆啡酒店(天津站津湾广场店)</t>
+          <t>维也纳国际酒店(天津站滨江道步行街店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3242,7 +3238,7 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3265,37 +3261,125 @@
         <v>30</v>
       </c>
       <c r="O31" t="n">
+        <v>20</v>
+      </c>
+      <c r="P31" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>30</v>
+      </c>
+      <c r="R31" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="n">
+        <v>20</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>7249997748999555075</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>汇通百达网络科技（上海）有限公司</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>津河省区</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>津东片区</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>7582047719217170486</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>喆啡酒店(天津站津湾广场店)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>喆啡酒店(天津站津湾广场店)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>已认证</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>115</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>提质量</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>30</v>
+      </c>
+      <c r="N32" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" t="n">
         <v>25</v>
       </c>
-      <c r="P31" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>30</v>
-      </c>
-      <c r="R31" t="n">
-        <v>30</v>
-      </c>
-      <c r="S31" t="n">
-        <v>20</v>
-      </c>
-      <c r="T31" t="n">
-        <v>20</v>
-      </c>
-      <c r="U31" t="inlineStr">
+      <c r="P32" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>30</v>
+      </c>
+      <c r="R32" t="n">
+        <v>30</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="n">
+        <v>20</v>
+      </c>
+      <c r="U32" t="inlineStr">
         <is>
           <t>7249997748999555075</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>汇通百达网络科技（上海）有限公司</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V31"/>
-  <conditionalFormatting sqref="H2:H31">
+  <autoFilter ref="A1:V32"/>
+  <conditionalFormatting sqref="H2:H32">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -3307,7 +3391,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I31">
+  <conditionalFormatting sqref="I2:I32">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
